--- a/Tableau_tarif.xlsx
+++ b/Tableau_tarif.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tpmg2\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C550284E-263E-4E86-B540-637B7951F756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A89A609-E81B-476D-B29A-AF3F56089970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{CC2AB062-ACCB-45F0-9F3E-84C3B8B3A0C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CC2AB062-ACCB-45F0-9F3E-84C3B8B3A0C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t>kms</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Laval</t>
   </si>
   <si>
-    <t>Aéroport de nantes</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -119,15 +116,9 @@
     <t>Noyen</t>
   </si>
   <si>
-    <t>La suze</t>
-  </si>
-  <si>
     <t>Segré</t>
   </si>
   <si>
-    <t>Château gontier</t>
-  </si>
-  <si>
     <t>Chateauneuf - sur- Sarthe</t>
   </si>
   <si>
@@ -161,12 +152,6 @@
     <t>Angers par départementale</t>
   </si>
   <si>
-    <t>Bouere</t>
-  </si>
-  <si>
-    <t>Grez en bouere</t>
-  </si>
-  <si>
     <t>Ballée</t>
   </si>
   <si>
@@ -192,6 +177,27 @@
   </si>
   <si>
     <t>Destination depuis la gare de Sablé</t>
+  </si>
+  <si>
+    <t>La Suze</t>
+  </si>
+  <si>
+    <t>Château Gontier</t>
+  </si>
+  <si>
+    <t>Grez en Bouère</t>
+  </si>
+  <si>
+    <t>Bouère</t>
+  </si>
+  <si>
+    <t>Aéroport de Nantes</t>
+  </si>
+  <si>
+    <t>Tarif 2</t>
+  </si>
+  <si>
+    <t>Tarif 1</t>
   </si>
 </sst>
 </file>
@@ -588,9 +594,9 @@
     <col min="8" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -598,10 +604,16 @@
       <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>59</v>
@@ -610,9 +622,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>52</v>
@@ -621,9 +633,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3">
         <v>65</v>
@@ -632,9 +644,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3">
         <v>52</v>
@@ -643,29 +655,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="3">
-        <v>4.0999999999999996</v>
+      <c r="B6" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="1">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="3">
-        <v>3.8</v>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="1">
+        <v>15</v>
+      </c>
+      <c r="E7" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -676,7 +700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -687,9 +711,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B10" s="3">
         <v>164</v>
@@ -698,7 +722,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -709,7 +733,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -720,7 +744,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -731,7 +755,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
@@ -742,7 +766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
@@ -753,31 +777,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>15</v>
+      </c>
+      <c r="E17" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B17" s="3">
-        <v>3</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="B18" s="3">
         <v>11.7</v>
@@ -786,9 +819,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="3">
         <v>15.4</v>
@@ -797,9 +830,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="3">
         <v>9.6</v>
@@ -808,9 +841,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="3">
         <v>15.7</v>
@@ -819,9 +852,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="3">
         <v>7.2</v>
@@ -830,9 +863,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="3">
         <v>22.1</v>
@@ -841,9 +874,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" s="3">
         <v>89</v>
@@ -852,9 +885,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="3">
         <v>122</v>
@@ -863,9 +896,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" s="3">
         <v>23.6</v>
@@ -874,9 +907,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="3">
         <v>19.399999999999999</v>
@@ -885,9 +918,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="3">
         <v>18.8</v>
@@ -896,9 +929,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B29" s="3">
         <v>31.3</v>
@@ -907,9 +940,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" s="3">
         <v>54</v>
@@ -918,9 +951,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B31" s="3">
         <v>32</v>
@@ -929,9 +962,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B32" s="3">
         <v>28</v>
@@ -942,7 +975,7 @@
     </row>
     <row r="33" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B33" s="3">
         <v>103</v>
@@ -953,7 +986,7 @@
     </row>
     <row r="34" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B34" s="3">
         <v>25</v>
@@ -964,7 +997,7 @@
     </row>
     <row r="35" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B35" s="3">
         <v>13.4</v>
@@ -975,7 +1008,7 @@
     </row>
     <row r="36" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B36" s="3">
         <v>21</v>
@@ -986,7 +1019,7 @@
     </row>
     <row r="37" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B37" s="3">
         <v>13</v>
@@ -997,7 +1030,7 @@
     </row>
     <row r="38" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B38" s="3">
         <v>11</v>
@@ -1008,7 +1041,7 @@
     </row>
     <row r="39" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B39" s="3">
         <v>14</v>
@@ -1019,7 +1052,7 @@
     </row>
     <row r="40" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B40" s="3">
         <v>17</v>
@@ -1030,7 +1063,7 @@
     </row>
     <row r="41" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B41" s="3">
         <v>15</v>
@@ -1041,7 +1074,7 @@
     </row>
     <row r="42" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B42" s="3">
         <v>10</v>
@@ -1052,7 +1085,7 @@
     </row>
     <row r="43" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B43" s="3">
         <v>4.4000000000000004</v>
@@ -1063,7 +1096,7 @@
     </row>
     <row r="44" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B44" s="3">
         <v>17</v>
@@ -1074,7 +1107,7 @@
     </row>
     <row r="45" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B45" s="3">
         <v>25</v>
@@ -1085,7 +1118,7 @@
     </row>
     <row r="46" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B46" s="3">
         <v>17</v>
@@ -1096,7 +1129,7 @@
     </row>
     <row r="47" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B47" s="3">
         <v>17.2</v>
@@ -1107,7 +1140,7 @@
     </row>
     <row r="48" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B48" s="3">
         <v>20</v>
